--- a/data/MK_YFINANCE_DATA_20260617.xlsx
+++ b/data/MK_YFINANCE_DATA_20260617.xlsx
@@ -20579,10 +20579,10 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>8856.59</v>
+        <v>8864.24</v>
       </c>
       <c r="G381" t="n">
-        <v>8856.59</v>
+        <v>8864.24</v>
       </c>
       <c r="H381" t="n">
         <v>8622.129999999999</v>
@@ -20595,15 +20595,15 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>554.95K</t>
+          <t>565.15K</t>
         </is>
       </c>
       <c r="L381" t="n">
-        <v>0.0149</v>
+        <v>0.0158</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260617',8856.59,8856.59,8622.13,8872.18,8605.66,'554.95K',0.0149,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260617',8864.24,8864.24,8622.13,8872.18,8605.66,'565.15K',0.0158,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -22061,10 +22061,10 @@
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1415.8</v>
+        <v>1416.97</v>
       </c>
       <c r="G409" t="n">
-        <v>1415.8</v>
+        <v>1416.97</v>
       </c>
       <c r="H409" t="n">
         <v>1372.13</v>
@@ -22077,15 +22077,15 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>197.00K</t>
+          <t>203.66K</t>
         </is>
       </c>
       <c r="L409" t="n">
-        <v>0.0964</v>
+        <v>0.0973</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260617',1415.8,1415.8,1372.13,1418.39,1370.26,'197.00K',0.0964,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260617',1416.97,1416.97,1372.13,1418.39,1370.26,'203.66K',0.0973,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -23596,10 +23596,10 @@
         </is>
       </c>
       <c r="F438" t="n">
-        <v>1030.98</v>
+        <v>1031.96</v>
       </c>
       <c r="G438" t="n">
-        <v>1030.98</v>
+        <v>1031.96</v>
       </c>
       <c r="H438" t="n">
         <v>1019.88</v>
@@ -23612,15 +23612,15 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>558.72K</t>
+          <t>564.71K</t>
         </is>
       </c>
       <c r="L438" t="n">
-        <v>-0.0029</v>
+        <v>-0.002</v>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260617',1030.98,1030.98,1019.88,1039.55,1008.57,'558.72K',-0.0029,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260617',1031.96,1031.96,1019.88,1039.55,1008.57,'564.71K',-0.002,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -31784,10 +31784,10 @@
         </is>
       </c>
       <c r="F600" t="n">
-        <v>1512.65</v>
+        <v>1511.28</v>
       </c>
       <c r="G600" t="n">
-        <v>1512.65</v>
+        <v>1511.28</v>
       </c>
       <c r="H600" t="n">
         <v>1508.32</v>
@@ -31800,11 +31800,11 @@
       </c>
       <c r="K600" t="inlineStr"/>
       <c r="L600" t="n">
-        <v>-0.0004</v>
+        <v>-0.0013</v>
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260617',1512.65,1512.65,1508.32,1515.28,1508.32,NULL,-0.0004,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260617',1511.28,1511.28,1508.32,1515.28,1508.32,NULL,-0.0013,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -31833,10 +31833,10 @@
         </is>
       </c>
       <c r="F601" t="n">
-        <v>223.99</v>
+        <v>223.82</v>
       </c>
       <c r="G601" t="n">
-        <v>223.99</v>
+        <v>223.82</v>
       </c>
       <c r="H601" t="n">
         <v>224</v>
@@ -31851,7 +31851,7 @@
       <c r="L601" t="inlineStr"/>
       <c r="M601" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260617',223.99,223.99,224.0,224.34,223.58,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260617',223.82,223.82,224.0,224.34,223.58,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -33495,10 +33495,10 @@
         </is>
       </c>
       <c r="F635" t="n">
-        <v>9.417</v>
+        <v>9.411</v>
       </c>
       <c r="G635" t="n">
-        <v>9.417</v>
+        <v>9.411</v>
       </c>
       <c r="H635" t="n">
         <v>9.381</v>
@@ -33511,11 +33511,11 @@
       </c>
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="n">
-        <v>-0.0014</v>
+        <v>-0.002</v>
       </c>
       <c r="M635" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260617',9.417,9.417,9.381,9.429,9.381,NULL,-0.0014,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260617',9.411,9.411,9.381,9.429,9.381,NULL,-0.002,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -36725,10 +36725,10 @@
         </is>
       </c>
       <c r="F701" t="n">
-        <v>75.27</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="G701" t="n">
-        <v>75.27</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="H701" t="n">
         <v>75.72</v>
@@ -36741,11 +36741,11 @@
       </c>
       <c r="K701" t="inlineStr"/>
       <c r="L701" t="n">
-        <v>-0.0103</v>
+        <v>-0.0166</v>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260617',75.27,75.27,75.72,76.06,74.46,NULL,-0.0103,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260617',74.79,74.79,75.72,76.06,74.46,NULL,-0.0166,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -38468,10 +38468,10 @@
         </is>
       </c>
       <c r="F734" t="n">
-        <v>4344.6</v>
+        <v>4348.6</v>
       </c>
       <c r="G734" t="n">
-        <v>4344.6</v>
+        <v>4348.6</v>
       </c>
       <c r="H734" t="n">
         <v>4352.6</v>
@@ -38484,15 +38484,15 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>15.56K</t>
+          <t>16.51K</t>
         </is>
       </c>
       <c r="L734" t="n">
-        <v>0.0032</v>
+        <v>0.0041</v>
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260617',4344.6,4344.6,4352.6,4369.8,4337.1,'15.56K',0.0032,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260617',4348.6,4348.6,4352.6,4369.8,4337.1,'16.51K',0.0041,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40109,10 +40109,10 @@
         </is>
       </c>
       <c r="F765" t="n">
-        <v>69998.06</v>
+        <v>69902.25</v>
       </c>
       <c r="G765" t="n">
-        <v>69998.06</v>
+        <v>69902.25</v>
       </c>
       <c r="H765" t="n">
         <v>69005.88</v>
@@ -40125,11 +40125,11 @@
       </c>
       <c r="K765" t="inlineStr"/>
       <c r="L765" t="n">
-        <v>0.0086</v>
+        <v>0.0072</v>
       </c>
       <c r="M765" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260617',69998.06,69998.06,69005.88,70125.75,68985.63,NULL,0.0086,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260617',69902.25,69902.25,69005.88,70125.75,68985.63,NULL,0.0072,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -43418,27 +43418,27 @@
         </is>
       </c>
       <c r="F830" t="n">
-        <v>99.56</v>
+        <v>99.55</v>
       </c>
       <c r="G830" t="n">
-        <v>99.56</v>
+        <v>99.55</v>
       </c>
       <c r="H830" t="n">
         <v>99.52</v>
       </c>
       <c r="I830" t="n">
-        <v>99.56</v>
+        <v>99.58</v>
       </c>
       <c r="J830" t="n">
         <v>99.48999999999999</v>
       </c>
       <c r="K830" t="inlineStr"/>
       <c r="L830" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="M830" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260617',99.56,99.56,99.52,99.56,99.49,NULL,0.0002,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260617',99.55,99.55,99.52,99.58,99.49,NULL,0.0001,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46648,10 +46648,10 @@
         </is>
       </c>
       <c r="F896" t="n">
-        <v>3.252</v>
+        <v>3.234</v>
       </c>
       <c r="G896" t="n">
-        <v>3.252</v>
+        <v>3.234</v>
       </c>
       <c r="H896" t="n">
         <v>3.257</v>
@@ -46660,15 +46660,15 @@
         <v>3.259</v>
       </c>
       <c r="J896" t="n">
-        <v>3.233</v>
+        <v>3.23</v>
       </c>
       <c r="K896" t="inlineStr"/>
       <c r="L896" t="n">
-        <v>0.004</v>
+        <v>-0.0015</v>
       </c>
       <c r="M896" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260617',3.252,3.252,3.257,3.259,3.233,NULL,0.004,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260617',3.234,3.234,3.257,3.259,3.23,NULL,-0.0015,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48263,10 +48263,10 @@
         </is>
       </c>
       <c r="F929" t="n">
-        <v>70.31</v>
+        <v>70.33</v>
       </c>
       <c r="G929" t="n">
-        <v>70.31</v>
+        <v>70.33</v>
       </c>
       <c r="H929" t="n">
         <v>70.14</v>
@@ -48279,11 +48279,11 @@
       </c>
       <c r="K929" t="inlineStr"/>
       <c r="L929" t="n">
-        <v>0.0058</v>
+        <v>0.0062</v>
       </c>
       <c r="M929" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260617',70.31,70.31,70.14,70.62,69.86,NULL,0.0058,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260617',70.33,70.33,70.14,70.62,69.86,NULL,0.0062,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
